--- a/ResourcesPH/ExcelTemplateForOutletCreation.xlsx
+++ b/ResourcesPH/ExcelTemplateForOutletCreation.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="152">
   <si>
     <t>Outlet Code</t>
   </si>
@@ -385,6 +385,96 @@
   </si>
   <si>
     <t>03118003000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLEA82C</t>
+  </si>
+  <si>
+    <t>03352680500</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL1452E</t>
+  </si>
+  <si>
+    <t>03353570600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL45895</t>
+  </si>
+  <si>
+    <t>03354378600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL686DE</t>
+  </si>
+  <si>
+    <t>03556248000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLAA984</t>
+  </si>
+  <si>
+    <t>03557931300</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL634FA</t>
+  </si>
+  <si>
+    <t>03559240100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL6808D</t>
+  </si>
+  <si>
+    <t>03984647400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLFBDC5</t>
+  </si>
+  <si>
+    <t>03987414100</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL76C6E</t>
+  </si>
+  <si>
+    <t>03989667400</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL57A90</t>
+  </si>
+  <si>
+    <t>03302913800</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLFA149</t>
+  </si>
+  <si>
+    <t>03303907600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL3714B</t>
+  </si>
+  <si>
+    <t>03304512200</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL4287C</t>
+  </si>
+  <si>
+    <t>03750231600</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL6AD82</t>
+  </si>
+  <si>
+    <t>03752552000</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL16938</t>
+  </si>
+  <si>
+    <t>03753948200</t>
   </si>
 </sst>
 </file>
@@ -1065,7 +1155,7 @@
     </row>
     <row r="2" spans="1:71" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
-        <v>116</v>
+        <v>146</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>84</v>
@@ -1095,7 +1185,7 @@
         <v>24.778867194283279</v>
       </c>
       <c r="Q2" s="4" t="n">
-        <v>24.77214540293758</v>
+        <v>24.80633534988221</v>
       </c>
       <c r="R2" s="8" t="s">
         <v>75</v>
@@ -1151,7 +1241,7 @@
       </c>
       <c r="AW2" s="5"/>
       <c r="AY2" s="12" t="s">
-        <v>117</v>
+        <v>147</v>
       </c>
       <c r="AZ2" s="11" t="s">
         <v>94</v>
@@ -1193,7 +1283,7 @@
     </row>
     <row r="3" spans="1:71" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
-        <v>118</v>
+        <v>148</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>84</v>
@@ -1223,7 +1313,7 @@
         <v>24.473190244254056</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>24.746053921347666</v>
+        <v>24.276930207904577</v>
       </c>
       <c r="R3" s="8" t="s">
         <v>75</v>
@@ -1279,7 +1369,7 @@
       </c>
       <c r="AW3" s="5"/>
       <c r="AY3" s="12" t="s">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="AZ3" s="11" t="s">
         <v>94</v>
@@ -1321,7 +1411,7 @@
     </row>
     <row r="4" spans="1:71" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>84</v>
@@ -1351,7 +1441,7 @@
         <v>24.955290746872056</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>24.198750530278136</v>
+        <v>24.578619749541186</v>
       </c>
       <c r="R4" s="8" t="s">
         <v>75</v>
@@ -1407,7 +1497,7 @@
       </c>
       <c r="AW4" s="5"/>
       <c r="AY4" s="12" t="s">
-        <v>121</v>
+        <v>151</v>
       </c>
       <c r="AZ4" s="11" t="s">
         <v>94</v>
